--- a/mapping/impix/S3_정제규칙_검토서_IMPIX.xlsx
+++ b/mapping/impix/S3_정제규칙_검토서_IMPIX.xlsx
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>완료 기준 6/7 충족(증분은 다음 단계)</t>
+          <t>완료 기준 7/8 충족(증분은 다음 단계)</t>
         </is>
       </c>
     </row>
